--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/ALABAMA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/ALABAMA_2017.xlsx
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C140">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C245">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C611">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C633">
@@ -14827,7 +14827,7 @@
         <v>71</v>
       </c>
       <c r="D804">
-        <v>0.009290761580738027</v>
+        <v>0.009290761580738029</v>
       </c>
     </row>
     <row r="805">
